--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FCE9D8-C52F-4CBB-BFB2-7CA21F6D74C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FEEB06-2F49-49D6-AD80-A727E168C01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -369,9 +369,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -855,49 +855,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <v>12618749</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
@@ -909,22 +909,22 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FEEB06-2F49-49D6-AD80-A727E168C01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C61372-0816-4AB1-B914-62A8916C35B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -202,6 +202,15 @@
   </si>
   <si>
     <t>On this day,I have done my revison of program</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>today I play cricket and complete my notes</t>
   </si>
 </sst>
 </file>
@@ -1016,27 +1025,51 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="10" t="str">
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>46250</v>
+      </c>
+      <c r="B7" s="9">
+        <v>380</v>
+      </c>
+      <c r="C7" s="9">
+        <v>55</v>
+      </c>
+      <c r="D7" s="9">
+        <v>80</v>
+      </c>
+      <c r="E7" s="9">
+        <v>95</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>120</v>
+      </c>
+      <c r="I7" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="10" t="str">
+        <v>730</v>
+      </c>
+      <c r="J7" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="12"/>
+        <v>710</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C61372-0816-4AB1-B914-62A8916C35B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B0AA0B-7374-4F7D-B438-C10E7FEC4D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,6 +211,12 @@
   </si>
   <si>
     <t>today I play cricket and complete my notes</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Good day overall,today I know the oops concept and python .</t>
   </si>
 </sst>
 </file>
@@ -1071,27 +1077,51 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10" t="str">
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B8" s="9">
+        <v>400</v>
+      </c>
+      <c r="C8" s="9">
+        <v>60</v>
+      </c>
+      <c r="D8" s="9">
+        <v>70</v>
+      </c>
+      <c r="E8" s="9">
+        <v>100</v>
+      </c>
+      <c r="F8" s="9">
+        <v>250</v>
+      </c>
+      <c r="G8" s="9">
+        <v>5</v>
+      </c>
+      <c r="H8" s="9">
+        <v>120</v>
+      </c>
+      <c r="I8" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="12"/>
+        <v>440</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B0AA0B-7374-4F7D-B438-C10E7FEC4D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CE7717-6968-4669-B9F2-DC53DADA77A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,9 @@
   <si>
     <t>Good day overall,today I know the oops concept and python .</t>
   </si>
+  <si>
+    <t>today I slove real world problem by using c++</t>
+  </si>
 </sst>
 </file>
 
@@ -357,7 +360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -387,6 +390,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -917,7 +923,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="13">
-        <v>46255</v>
+        <v>46249</v>
       </c>
       <c r="G3" s="13">
         <v>46286</v>
@@ -1123,27 +1129,51 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10" t="str">
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B9" s="9">
+        <v>410</v>
+      </c>
+      <c r="C9" s="9">
+        <v>50</v>
+      </c>
+      <c r="D9" s="9">
+        <v>90</v>
+      </c>
+      <c r="E9" s="9">
+        <v>100</v>
+      </c>
+      <c r="F9" s="9">
+        <v>250</v>
+      </c>
+      <c r="G9" s="9">
+        <v>5</v>
+      </c>
+      <c r="H9" s="9">
+        <v>80</v>
+      </c>
+      <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="10" t="str">
+        <v>980</v>
+      </c>
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
+        <v>460</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CE7717-6968-4669-B9F2-DC53DADA77A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6657FA-68FD-452A-A76B-73FCF626C2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t>today I slove real world problem by using c++</t>
+  </si>
+  <si>
+    <t>today I learn new in advance database program</t>
   </si>
 </sst>
 </file>
@@ -1175,27 +1178,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10" t="str">
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B10" s="9">
+        <v>420</v>
+      </c>
+      <c r="C10" s="9">
+        <v>55</v>
+      </c>
+      <c r="D10" s="9">
+        <v>110</v>
+      </c>
+      <c r="E10" s="9">
+        <v>30</v>
+      </c>
+      <c r="F10" s="9">
+        <v>250</v>
+      </c>
+      <c r="G10" s="9">
+        <v>5</v>
+      </c>
+      <c r="H10" s="9">
+        <v>50</v>
+      </c>
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="10" t="str">
+        <v>915</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="12"/>
+        <v>525</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6657FA-68FD-452A-A76B-73FCF626C2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A00161C-9991-410A-9A47-826F878C1A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,12 @@
   </si>
   <si>
     <t>today I learn new in advance database program</t>
+  </si>
+  <si>
+    <t>today I tried bcoz back to back classes but learn new things</t>
+  </si>
+  <si>
+    <t>today I learn Cisco packet tracer in networking</t>
   </si>
 </sst>
 </file>
@@ -1224,49 +1230,97 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10" t="str">
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B11" s="9">
+        <v>400</v>
+      </c>
+      <c r="C11" s="9">
+        <v>65</v>
+      </c>
+      <c r="D11" s="9">
+        <v>80</v>
+      </c>
+      <c r="E11" s="9">
+        <v>100</v>
+      </c>
+      <c r="F11" s="9">
+        <v>300</v>
+      </c>
+      <c r="G11" s="9">
+        <v>6</v>
+      </c>
+      <c r="H11" s="9">
+        <v>40</v>
+      </c>
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
+        <v>985</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="12"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
+        <v>455</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B12" s="9">
+        <v>480</v>
+      </c>
+      <c r="C12" s="9">
+        <v>50</v>
+      </c>
+      <c r="D12" s="9">
+        <v>150</v>
+      </c>
+      <c r="E12" s="9">
+        <v>150</v>
+      </c>
+      <c r="F12" s="9">
+        <v>300</v>
+      </c>
+      <c r="G12" s="9">
+        <v>6</v>
+      </c>
+      <c r="H12" s="9">
+        <v>55</v>
+      </c>
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="12"/>
+        <v>255</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A00161C-9991-410A-9A47-826F878C1A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499E4612-0D4D-44F3-8F86-7257CD3F7C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>today I learn Cisco packet tracer in networking</t>
+  </si>
+  <si>
+    <t>today class off So I complete my notes and revision the concept</t>
   </si>
 </sst>
 </file>
@@ -1322,27 +1325,51 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B13" s="9">
+        <v>480</v>
+      </c>
+      <c r="C13" s="9">
+        <v>30</v>
+      </c>
+      <c r="D13" s="9">
+        <v>180</v>
+      </c>
+      <c r="E13" s="9">
+        <v>100</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>120</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
+        <v>910</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
+        <v>530</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499E4612-0D4D-44F3-8F86-7257CD3F7C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01F7F35-2123-4A6A-B408-CE44517272F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>today class off So I complete my notes and revision the concept</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>today I play cricket and feel so happy</t>
   </si>
 </sst>
 </file>
@@ -1371,27 +1377,51 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B14" s="9">
+        <v>450</v>
+      </c>
+      <c r="C14" s="9">
+        <v>20</v>
+      </c>
+      <c r="D14" s="9">
+        <v>200</v>
+      </c>
+      <c r="E14" s="9">
+        <v>60</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>100</v>
+      </c>
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>830</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
+        <v>610</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01F7F35-2123-4A6A-B408-CE44517272F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E61F66-CA7C-4553-82C3-ED55CC6BEDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t>today I play cricket and feel so happy</t>
+  </si>
+  <si>
+    <t>today learn class and function in python and also c++</t>
+  </si>
+  <si>
+    <t>today I learn about the type mindset and leadership</t>
   </si>
 </sst>
 </file>
@@ -1423,49 +1429,97 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B15" s="9">
+        <v>360</v>
+      </c>
+      <c r="C15" s="9">
+        <v>60</v>
+      </c>
+      <c r="D15" s="9">
+        <v>100</v>
+      </c>
+      <c r="E15" s="9">
+        <v>100</v>
+      </c>
+      <c r="F15" s="9">
+        <v>250</v>
+      </c>
+      <c r="G15" s="9">
+        <v>5</v>
+      </c>
+      <c r="H15" s="9">
+        <v>90</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>960</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B16" s="9">
+        <v>400</v>
+      </c>
+      <c r="C16" s="9">
+        <v>50</v>
+      </c>
+      <c r="D16" s="9">
+        <v>80</v>
+      </c>
+      <c r="E16" s="9">
+        <v>100</v>
+      </c>
+      <c r="F16" s="9">
+        <v>250</v>
+      </c>
+      <c r="G16" s="9">
+        <v>5</v>
+      </c>
+      <c r="H16" s="9">
+        <v>50</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>930</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
+        <v>510</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E61F66-CA7C-4553-82C3-ED55CC6BEDAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B59982C-7391-4051-A4F2-A26A64C59B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>today I learn about the type mindset and leadership</t>
+  </si>
+  <si>
+    <t>today I visit the lpu sports indoor stadium and full enjoyed</t>
   </si>
 </sst>
 </file>
@@ -1521,27 +1524,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B17" s="9">
+        <v>420</v>
+      </c>
+      <c r="C17" s="9">
+        <v>40</v>
+      </c>
+      <c r="D17" s="9">
+        <v>120</v>
+      </c>
+      <c r="E17" s="9">
+        <v>60</v>
+      </c>
+      <c r="F17" s="9">
+        <v>250</v>
+      </c>
+      <c r="G17" s="9">
+        <v>5</v>
+      </c>
+      <c r="H17" s="9">
+        <v>60</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
+        <v>490</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B59982C-7391-4051-A4F2-A26A64C59B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F623C622-538B-4416-A57F-2B40A0246566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>today I visit the lpu sports indoor stadium and full enjoyed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">today back to back class but overall good </t>
   </si>
 </sst>
 </file>
@@ -1570,27 +1573,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B18" s="9">
+        <v>400</v>
+      </c>
+      <c r="C18" s="9">
+        <v>60</v>
+      </c>
+      <c r="D18" s="9">
+        <v>180</v>
+      </c>
+      <c r="E18" s="9">
+        <v>90</v>
+      </c>
+      <c r="F18" s="9">
+        <v>300</v>
+      </c>
+      <c r="G18" s="9">
+        <v>6</v>
+      </c>
+      <c r="H18" s="9">
+        <v>80</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+        <v>330</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F623C622-538B-4416-A57F-2B40A0246566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9ED700B-028E-49EC-8775-8838212DCA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t xml:space="preserve">today back to back class but overall good </t>
+  </si>
+  <si>
+    <t xml:space="preserve">In communicatipon class we do the group discussion </t>
   </si>
 </sst>
 </file>
@@ -1619,27 +1622,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B19" s="9">
+        <v>420</v>
+      </c>
+      <c r="C19" s="9">
+        <v>50</v>
+      </c>
+      <c r="D19" s="9">
+        <v>240</v>
+      </c>
+      <c r="E19" s="9">
+        <v>100</v>
+      </c>
+      <c r="F19" s="9">
+        <v>300</v>
+      </c>
+      <c r="G19" s="9">
+        <v>6</v>
+      </c>
+      <c r="H19" s="9">
+        <v>60</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
+        <v>270</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9ED700B-028E-49EC-8775-8838212DCA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9479C6B5-4074-454E-B262-7EE5E4CD761C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t xml:space="preserve">In communicatipon class we do the group discussion </t>
+  </si>
+  <si>
+    <t>today extra class then I go library and doing my work</t>
   </si>
 </sst>
 </file>
@@ -1668,27 +1671,51 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B20" s="9">
+        <v>450</v>
+      </c>
+      <c r="C20" s="9">
+        <v>60</v>
+      </c>
+      <c r="D20" s="9">
+        <v>180</v>
+      </c>
+      <c r="E20" s="9">
+        <v>120</v>
+      </c>
+      <c r="F20" s="9">
+        <v>50</v>
+      </c>
+      <c r="G20" s="9">
+        <v>1</v>
+      </c>
+      <c r="H20" s="9">
+        <v>90</v>
+      </c>
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
+        <v>490</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9479C6B5-4074-454E-B262-7EE5E4CD761C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6E61E0-96CB-48B5-B8E1-AC9A526FBB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>today extra class then I go library and doing my work</t>
+  </si>
+  <si>
+    <t>I complete my study and then I watch the web series</t>
   </si>
 </sst>
 </file>
@@ -1717,27 +1720,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B21" s="9">
+        <v>450</v>
+      </c>
+      <c r="C21" s="9">
+        <v>30</v>
+      </c>
+      <c r="D21" s="9">
+        <v>240</v>
+      </c>
+      <c r="E21" s="9">
+        <v>180</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>60</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>960</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
+        <v>480</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6E61E0-96CB-48B5-B8E1-AC9A526FBB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A218E7-082F-4561-8DB1-6623B6CDE646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>I complete my study and then I watch the web series</t>
+  </si>
+  <si>
+    <t>In communicatipon class I talk about th current affairs</t>
   </si>
 </sst>
 </file>
@@ -1766,27 +1769,51 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B22" s="9">
+        <v>360</v>
+      </c>
+      <c r="C22" s="9">
+        <v>70</v>
+      </c>
+      <c r="D22" s="9">
+        <v>100</v>
+      </c>
+      <c r="E22" s="9">
+        <v>100</v>
+      </c>
+      <c r="F22" s="9">
+        <v>5</v>
+      </c>
+      <c r="G22" s="9">
+        <v>5</v>
+      </c>
+      <c r="H22" s="9">
+        <v>60</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>695</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
+        <v>745</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A218E7-082F-4561-8DB1-6623B6CDE646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A6B535-0FFD-4391-B562-C68D85091D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -261,7 +261,10 @@
     <t>I complete my study and then I watch the web series</t>
   </si>
   <si>
-    <t>In communicatipon class I talk about th current affairs</t>
+    <t>In communication class I talk about th current affairs</t>
+  </si>
+  <si>
+    <t>today overall feels good and productive by adpat the concept</t>
   </si>
 </sst>
 </file>
@@ -429,12 +432,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -918,49 +921,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="17">
         <v>12618749</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
@@ -972,22 +975,22 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1213,7 +1216,7 @@
       <c r="M9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N9" s="14" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1627,7 +1630,7 @@
       <c r="M18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="17" t="s">
+      <c r="N18" s="14" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1786,7 +1789,7 @@
         <v>100</v>
       </c>
       <c r="F22" s="9">
-        <v>5</v>
+        <v>250</v>
       </c>
       <c r="G22" s="9">
         <v>5</v>
@@ -1796,11 +1799,11 @@
       </c>
       <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v>695</v>
+        <v>940</v>
       </c>
       <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v>745</v>
+        <v>500</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>49</v>
@@ -1815,27 +1818,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B23" s="9">
+        <v>400</v>
+      </c>
+      <c r="C23" s="9">
+        <v>50</v>
+      </c>
+      <c r="D23" s="9">
+        <v>180</v>
+      </c>
+      <c r="E23" s="9">
+        <v>100</v>
+      </c>
+      <c r="F23" s="9">
+        <v>250</v>
+      </c>
+      <c r="G23" s="9">
+        <v>5</v>
+      </c>
+      <c r="H23" s="9">
+        <v>90</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
+        <v>370</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A6B535-0FFD-4391-B562-C68D85091D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECD2D5C-677B-4D63-8F35-6440A9C744B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>today overall feels good and productive by adpat the concept</t>
+  </si>
+  <si>
+    <t>I learn how to improve ours vocals and pronountiation .</t>
   </si>
 </sst>
 </file>
@@ -1864,27 +1867,51 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B24" s="9">
+        <v>380</v>
+      </c>
+      <c r="C24" s="9">
+        <v>40</v>
+      </c>
+      <c r="D24" s="9">
+        <v>220</v>
+      </c>
+      <c r="E24" s="9">
+        <v>80</v>
+      </c>
+      <c r="F24" s="9">
+        <v>250</v>
+      </c>
+      <c r="G24" s="9">
+        <v>5</v>
+      </c>
+      <c r="H24" s="9">
+        <v>70</v>
+      </c>
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECD2D5C-677B-4D63-8F35-6440A9C744B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9B71CC-0B63-4B09-8497-3EB896F61FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,12 @@
   </si>
   <si>
     <t>I learn how to improve ours vocals and pronountiation .</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">today not feel good and but also attend the classes </t>
   </si>
 </sst>
 </file>
@@ -1913,27 +1919,51 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B25" s="9">
+        <v>420</v>
+      </c>
+      <c r="C25" s="9">
+        <v>60</v>
+      </c>
+      <c r="D25" s="9">
+        <v>180</v>
+      </c>
+      <c r="E25" s="9">
+        <v>120</v>
+      </c>
+      <c r="F25" s="9">
+        <v>300</v>
+      </c>
+      <c r="G25" s="9">
+        <v>6</v>
+      </c>
+      <c r="H25" s="9">
+        <v>80</v>
+      </c>
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="12"/>
+        <v>280</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9B71CC-0B63-4B09-8497-3EB896F61FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78FCA4B-A3AD-4095-8741-B6187A57D629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t xml:space="preserve">today not feel good and but also attend the classes </t>
+  </si>
+  <si>
+    <t>today prepare for CA and mentor meeting also attend</t>
   </si>
 </sst>
 </file>
@@ -1965,27 +1968,51 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
+    <row r="26" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B26" s="9">
+        <v>320</v>
+      </c>
+      <c r="C26" s="9">
+        <v>40</v>
+      </c>
+      <c r="D26" s="9">
+        <v>250</v>
+      </c>
+      <c r="E26" s="9">
+        <v>100</v>
+      </c>
+      <c r="F26" s="9">
+        <v>300</v>
+      </c>
+      <c r="G26" s="9">
+        <v>6</v>
+      </c>
+      <c r="H26" s="9">
+        <v>60</v>
+      </c>
+      <c r="I26" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12"/>
+        <v>370</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78FCA4B-A3AD-4095-8741-B6187A57D629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703BEF0E-01B0-4673-8A64-A9565B69E3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>today prepare for CA and mentor meeting also attend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">today class off,so I done all the remaining the works </t>
   </si>
 </sst>
 </file>
@@ -2014,27 +2017,51 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B27" s="9">
+        <v>400</v>
+      </c>
+      <c r="C27" s="9">
+        <v>30</v>
+      </c>
+      <c r="D27" s="9">
+        <v>300</v>
+      </c>
+      <c r="E27" s="9">
+        <v>60</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0</v>
+      </c>
+      <c r="H27" s="9">
+        <v>40</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
+        <v>830</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
+        <v>610</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703BEF0E-01B0-4673-8A64-A9565B69E3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B8DD67-CD55-4EB7-8689-2A8AC2AAC79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t xml:space="preserve">today class off,so I done all the remaining the works </t>
+  </si>
+  <si>
+    <t>nice and productive day with no classes</t>
   </si>
 </sst>
 </file>
@@ -2063,27 +2066,51 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B28" s="9">
+        <v>420</v>
+      </c>
+      <c r="C28" s="9">
+        <v>10</v>
+      </c>
+      <c r="D28" s="9">
+        <v>240</v>
+      </c>
+      <c r="E28" s="9">
+        <v>100</v>
+      </c>
+      <c r="F28" s="9">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
+        <v>30</v>
+      </c>
+      <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
+        <v>800</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="12"/>
+        <v>640</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B8DD67-CD55-4EB7-8689-2A8AC2AAC79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF23597-1533-41C1-90D9-65F6308F9611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>nice and productive day with no classes</t>
+  </si>
+  <si>
+    <t>Monday is not funday so we study and aslo goes wells</t>
   </si>
 </sst>
 </file>
@@ -2112,27 +2115,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B29" s="9">
+        <v>360</v>
+      </c>
+      <c r="C29" s="9">
+        <v>60</v>
+      </c>
+      <c r="D29" s="9">
+        <v>100</v>
+      </c>
+      <c r="E29" s="9">
+        <v>100</v>
+      </c>
+      <c r="F29" s="9">
+        <v>250</v>
+      </c>
+      <c r="G29" s="9">
+        <v>250</v>
+      </c>
+      <c r="H29" s="9">
+        <v>70</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
+        <v>940</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
+        <v>500</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF23597-1533-41C1-90D9-65F6308F9611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D17E86-1B9D-4758-AF4B-0DA6D2FB556F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>Monday is not funday so we study and aslo goes wells</t>
+  </si>
+  <si>
+    <t>pretty balanced day with classes and study</t>
   </si>
 </sst>
 </file>
@@ -2135,7 +2138,7 @@
         <v>250</v>
       </c>
       <c r="G29" s="9">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="H29" s="9">
         <v>70</v>
@@ -2161,27 +2164,51 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B30" s="9">
+        <v>400</v>
+      </c>
+      <c r="C30" s="9">
+        <v>70</v>
+      </c>
+      <c r="D30" s="9">
+        <v>120</v>
+      </c>
+      <c r="E30" s="9">
+        <v>100</v>
+      </c>
+      <c r="F30" s="9">
+        <v>250</v>
+      </c>
+      <c r="G30" s="9">
+        <v>5</v>
+      </c>
+      <c r="H30" s="9">
+        <v>50</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
+        <v>990</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
+        <v>450</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D17E86-1B9D-4758-AF4B-0DA6D2FB556F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83228C91-946A-4CB8-B1F3-9E0957446F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>pretty balanced day with classes and study</t>
+  </si>
+  <si>
+    <t>today I learn shortcut to find the average and percentage .</t>
   </si>
 </sst>
 </file>
@@ -2210,27 +2213,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B31" s="9">
+        <v>420</v>
+      </c>
+      <c r="C31" s="9">
+        <v>80</v>
+      </c>
+      <c r="D31" s="9">
+        <v>220</v>
+      </c>
+      <c r="E31" s="9">
+        <v>60</v>
+      </c>
+      <c r="F31" s="9">
+        <v>250</v>
+      </c>
+      <c r="G31" s="9">
+        <v>5</v>
+      </c>
+      <c r="H31" s="9">
+        <v>60</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+        <v>350</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83228C91-946A-4CB8-B1F3-9E0957446F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60013A27-4208-449E-AA96-7232ED2DE4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>today I learn shortcut to find the average and percentage .</t>
+  </si>
+  <si>
+    <t>today we disscuss about problem statement in SIH</t>
   </si>
 </sst>
 </file>
@@ -2259,27 +2262,51 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B32" s="9">
+        <v>340</v>
+      </c>
+      <c r="C32" s="9">
+        <v>60</v>
+      </c>
+      <c r="D32" s="9">
+        <v>120</v>
+      </c>
+      <c r="E32" s="9">
+        <v>100</v>
+      </c>
+      <c r="F32" s="9">
+        <v>300</v>
+      </c>
+      <c r="G32" s="9">
+        <v>6</v>
+      </c>
+      <c r="H32" s="9">
+        <v>80</v>
+      </c>
+      <c r="I32" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J32" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
+        <v>440</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60013A27-4208-449E-AA96-7232ED2DE4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047ABB6C-BDA9-4F86-B653-D8415AA94150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,12 @@
   </si>
   <si>
     <t>today we disscuss about problem statement in SIH</t>
+  </si>
+  <si>
+    <t>Good day overall,but the schedule was quite full</t>
+  </si>
+  <si>
+    <t>nice and productive day with no classes but I go library for study.</t>
   </si>
 </sst>
 </file>
@@ -2308,49 +2314,97 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B33" s="9">
+        <v>420</v>
+      </c>
+      <c r="C33" s="9">
+        <v>50</v>
+      </c>
+      <c r="D33" s="9">
+        <v>180</v>
+      </c>
+      <c r="E33" s="9">
+        <v>120</v>
+      </c>
+      <c r="F33" s="9">
+        <v>300</v>
+      </c>
+      <c r="G33" s="9">
+        <v>6</v>
+      </c>
+      <c r="H33" s="9">
+        <v>60</v>
+      </c>
+      <c r="I33" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
+        <v>310</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B34" s="9">
+        <v>360</v>
+      </c>
+      <c r="C34" s="9">
+        <v>40</v>
+      </c>
+      <c r="D34" s="9">
+        <v>240</v>
+      </c>
+      <c r="E34" s="9">
+        <v>90</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>40</v>
+      </c>
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
+        <v>770</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
+        <v>670</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047ABB6C-BDA9-4F86-B653-D8415AA94150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89163FDE-0BAF-486E-96D3-C0B06CA956CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>nice and productive day with no classes but I go library for study.</t>
+  </si>
+  <si>
+    <t>all the notes and program for the next CA.</t>
   </si>
 </sst>
 </file>
@@ -2406,27 +2409,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B35" s="9">
+        <v>420</v>
+      </c>
+      <c r="C35" s="9">
+        <v>20</v>
+      </c>
+      <c r="D35" s="9">
+        <v>260</v>
+      </c>
+      <c r="E35" s="9">
+        <v>120</v>
+      </c>
+      <c r="F35" s="9">
+        <v>0</v>
+      </c>
+      <c r="G35" s="9">
+        <v>0</v>
+      </c>
+      <c r="H35" s="9">
+        <v>10</v>
+      </c>
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
+        <v>830</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
+        <v>610</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89163FDE-0BAF-486E-96D3-C0B06CA956CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D17E88-A621-4A92-B514-62ED67CE4B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>all the notes and program for the next CA.</t>
+  </si>
+  <si>
+    <t>today storytelling activity are performed by me and all good .</t>
   </si>
 </sst>
 </file>
@@ -2455,27 +2458,51 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B36" s="9">
+        <v>360</v>
+      </c>
+      <c r="C36" s="9">
+        <v>60</v>
+      </c>
+      <c r="D36" s="9">
+        <v>120</v>
+      </c>
+      <c r="E36" s="9">
+        <v>100</v>
+      </c>
+      <c r="F36" s="9">
+        <v>250</v>
+      </c>
+      <c r="G36" s="9">
+        <v>5</v>
+      </c>
+      <c r="H36" s="9">
+        <v>50</v>
+      </c>
+      <c r="I36" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
+        <v>940</v>
+      </c>
+      <c r="J36" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
+        <v>500</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D17E88-A621-4A92-B514-62ED67CE4B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B2C69F-14D5-44F3-8300-FDBCB78546FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>today storytelling activity are performed by me and all good .</t>
+  </si>
+  <si>
+    <t>overall days goes good but back to back classes schedule</t>
   </si>
 </sst>
 </file>
@@ -2504,27 +2507,51 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
+    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B37" s="9">
+        <v>400</v>
+      </c>
+      <c r="C37" s="9">
+        <v>50</v>
+      </c>
+      <c r="D37" s="9">
+        <v>180</v>
+      </c>
+      <c r="E37" s="9">
+        <v>100</v>
+      </c>
+      <c r="F37" s="9">
+        <v>250</v>
+      </c>
+      <c r="G37" s="9">
+        <v>5</v>
+      </c>
+      <c r="H37" s="9">
+        <v>60</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="14" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B2C69F-14D5-44F3-8300-FDBCB78546FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AC49BE-8780-449B-AB03-DFF1D114824A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>overall days goes good but back to back classes schedule</t>
+  </si>
+  <si>
+    <t>I learn file handling c++ and python programming .</t>
   </si>
 </sst>
 </file>
@@ -2553,27 +2556,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B38" s="9">
+        <v>420</v>
+      </c>
+      <c r="C38" s="9">
+        <v>70</v>
+      </c>
+      <c r="D38" s="9">
+        <v>240</v>
+      </c>
+      <c r="E38" s="9">
+        <v>30</v>
+      </c>
+      <c r="F38" s="9">
+        <v>250</v>
+      </c>
+      <c r="G38" s="9">
+        <v>5</v>
+      </c>
+      <c r="H38" s="9">
+        <v>70</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
+        <v>360</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AC49BE-8780-449B-AB03-DFF1D114824A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04EC06C-AC1E-4119-8807-419337DD25F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>I learn file handling c++ and python programming .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">today my mentor meeting and DHCP connections </t>
   </si>
 </sst>
 </file>
@@ -2602,27 +2605,51 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B39" s="9">
+        <v>420</v>
+      </c>
+      <c r="C39" s="9">
+        <v>80</v>
+      </c>
+      <c r="D39" s="9">
+        <v>100</v>
+      </c>
+      <c r="E39" s="9">
+        <v>90</v>
+      </c>
+      <c r="F39" s="9">
+        <v>300</v>
+      </c>
+      <c r="G39" s="9">
+        <v>6</v>
+      </c>
+      <c r="H39" s="9">
+        <v>60</v>
+      </c>
+      <c r="I39" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J39" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04EC06C-AC1E-4119-8807-419337DD25F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1475506-58B0-480D-81ED-CF5C3091B4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t xml:space="preserve">today my mentor meeting and DHCP connections </t>
+  </si>
+  <si>
+    <t>I learn and prepare for my ca of pel course</t>
   </si>
 </sst>
 </file>
@@ -2651,27 +2654,49 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B40" s="9">
+        <v>400</v>
+      </c>
+      <c r="C40" s="9">
+        <v>60</v>
+      </c>
+      <c r="D40" s="9">
+        <v>180</v>
+      </c>
+      <c r="E40" s="9">
+        <v>150</v>
+      </c>
+      <c r="F40" s="9">
+        <v>300</v>
+      </c>
+      <c r="G40" s="9">
+        <v>6</v>
+      </c>
+      <c r="H40" s="9">
+        <v>60</v>
+      </c>
+      <c r="I40" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
+        <v>290</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
+      <c r="N40" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1475506-58B0-480D-81ED-CF5C3091B4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABDCDB2-9F76-4ED1-BC1B-90DC78BCDECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="269" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>I learn and prepare for my ca of pel course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">today I start and thinking  about my new project </t>
   </si>
 </sst>
 </file>
@@ -2693,32 +2696,58 @@
       <c r="L40" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M40" s="11"/>
+      <c r="M40" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N40" s="12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
+    <row r="41" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B41" s="9">
+        <v>420</v>
+      </c>
+      <c r="C41" s="9">
+        <v>60</v>
+      </c>
+      <c r="D41" s="9">
+        <v>240</v>
+      </c>
+      <c r="E41" s="9">
+        <v>180</v>
+      </c>
+      <c r="F41" s="9">
+        <v>0</v>
+      </c>
+      <c r="G41" s="9">
+        <v>0</v>
+      </c>
+      <c r="H41" s="9">
+        <v>70</v>
+      </c>
+      <c r="I41" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
+        <v>970</v>
+      </c>
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
+        <v>470</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABDCDB2-9F76-4ED1-BC1B-90DC78BCDECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3538E35-98A0-46FD-90E9-34C569CA381A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="269" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t xml:space="preserve">today I start and thinking  about my new project </t>
+  </si>
+  <si>
+    <t>today I watch movies and start coding for my new project</t>
   </si>
 </sst>
 </file>
@@ -2749,27 +2752,51 @@
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B42" s="9">
+        <v>360</v>
+      </c>
+      <c r="C42" s="9">
+        <v>30</v>
+      </c>
+      <c r="D42" s="9">
+        <v>100</v>
+      </c>
+      <c r="E42" s="9">
+        <v>200</v>
+      </c>
+      <c r="F42" s="9">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9">
+        <v>0</v>
+      </c>
+      <c r="H42" s="9">
+        <v>90</v>
+      </c>
+      <c r="I42" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
+        <v>780</v>
+      </c>
+      <c r="J42" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
+        <v>660</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3538E35-98A0-46FD-90E9-34C569CA381A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F30BEFC-3B51-43E1-9BE7-047F0814FC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="269" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2798,27 +2798,51 @@
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
+    <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B43" s="9">
+        <v>420</v>
+      </c>
+      <c r="C43" s="9">
+        <v>60</v>
+      </c>
+      <c r="D43" s="9">
+        <v>100</v>
+      </c>
+      <c r="E43" s="9">
+        <v>150</v>
+      </c>
+      <c r="F43" s="9">
+        <v>250</v>
+      </c>
+      <c r="G43" s="9">
+        <v>5</v>
+      </c>
+      <c r="H43" s="9">
+        <v>70</v>
+      </c>
+      <c r="I43" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J43" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F30BEFC-3B51-43E1-9BE7-047F0814FC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D8BEE6-1176-4CE9-8C16-409F42FC6DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="269" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>today I watch movies and start coding for my new project</t>
+  </si>
+  <si>
+    <t>overall days goes good and add member in my project</t>
   </si>
 </sst>
 </file>
@@ -966,7 +969,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N400"/>
+  <dimension ref="A1:N399"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -1122,11 +1125,11 @@
         <v>180</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I68" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I67" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>1160</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J68" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J67" si="1">IF(I6="","",1440-I6)</f>
         <v>280</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -2841,7 +2844,7 @@
         <v>51</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -3382,11 +3385,11 @@
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
       <c r="I68" s="10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I68:I131" si="2">IF(SUM(B68:F68,H68)=0,"",SUM(B68:F68,H68))</f>
         <v/>
       </c>
       <c r="J68" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J68:J131" si="3">IF(I68="","",1440-I68)</f>
         <v/>
       </c>
       <c r="K68" s="11"/>
@@ -3404,11 +3407,11 @@
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
       <c r="I69" s="10" t="str">
-        <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J69" s="10" t="str">
-        <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K69" s="11"/>
@@ -4790,11 +4793,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I132:I195" si="4">IF(SUM(B132:F132,H132)=0,"",SUM(B132:F132,H132))</f>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J132:J195" si="5">IF(I132="","",1440-I132)</f>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4812,11 +4815,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" ref="I133:I196" si="4">IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" ref="J133:J196" si="5">IF(I133="","",1440-I133)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -6198,11 +6201,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I196:I259" si="6">IF(SUM(B196:F196,H196)=0,"",SUM(B196:F196,H196))</f>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J196:J259" si="7">IF(I196="","",1440-I196)</f>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6220,11 +6223,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" ref="I197:I260" si="6">IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" ref="J197:J260" si="7">IF(I197="","",1440-I197)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -7606,11 +7609,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I260:I323" si="8">IF(SUM(B260:F260,H260)=0,"",SUM(B260:F260,H260))</f>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J260:J323" si="9">IF(I260="","",1440-I260)</f>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7628,11 +7631,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" ref="I261:I324" si="8">IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" ref="J261:J324" si="9">IF(I261="","",1440-I261)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -9014,11 +9017,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I324:I387" si="10">IF(SUM(B324:F324,H324)=0,"",SUM(B324:F324,H324))</f>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J324:J387" si="11">IF(I324="","",1440-I324)</f>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -9036,11 +9039,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" ref="I325:I388" si="10">IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" ref="J325:J388" si="11">IF(I325="","",1440-I325)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -10422,11 +10425,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I388:I399" si="12">IF(SUM(B388:F388,H388)=0,"",SUM(B388:F388,H388))</f>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J388:J399" si="13">IF(I388="","",1440-I388)</f>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10444,11 +10447,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" ref="I389:I400" si="12">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10676,28 +10679,6 @@
       <c r="M399" s="11"/>
       <c r="N399" s="12"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A400" s="8"/>
-      <c r="B400" s="9"/>
-      <c r="C400" s="9"/>
-      <c r="D400" s="9"/>
-      <c r="E400" s="9"/>
-      <c r="F400" s="9"/>
-      <c r="G400" s="9"/>
-      <c r="H400" s="9"/>
-      <c r="I400" s="10" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J400" s="10" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K400" s="11"/>
-      <c r="L400" s="11"/>
-      <c r="M400" s="11"/>
-      <c r="N400" s="12"/>
-    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A4:N4"/>
@@ -10706,21 +10687,21 @@
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="B3:D3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J400">
+  <conditionalFormatting sqref="J6:J399">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K42 K43:K399" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L42 L43:L399" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M42 M43:M399" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D8BEE6-1176-4CE9-8C16-409F42FC6DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A87ED5-6701-4BC6-8E44-7ACA9CD9DD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="269" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,18 @@
   </si>
   <si>
     <t>overall days goes good and add member in my project</t>
+  </si>
+  <si>
+    <t>preparing for ca and mid-term test</t>
+  </si>
+  <si>
+    <t>quite a busy day with classes and study</t>
+  </si>
+  <si>
+    <t>today ca's of subject english and dbms,its goes very well</t>
+  </si>
+  <si>
+    <t xml:space="preserve">back to back classes with busy schedule </t>
   </si>
 </sst>
 </file>
@@ -2847,93 +2859,189 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
+    <row r="44" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B44" s="9">
+        <v>400</v>
+      </c>
+      <c r="C44" s="9">
+        <v>60</v>
+      </c>
+      <c r="D44" s="9">
+        <v>120</v>
+      </c>
+      <c r="E44" s="9">
+        <v>120</v>
+      </c>
+      <c r="F44" s="9">
+        <v>250</v>
+      </c>
+      <c r="G44" s="9">
+        <v>5</v>
+      </c>
+      <c r="H44" s="9">
+        <v>80</v>
+      </c>
+      <c r="I44" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
+        <v>410</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B45" s="9">
+        <v>420</v>
+      </c>
+      <c r="C45" s="9">
+        <v>50</v>
+      </c>
+      <c r="D45" s="9">
+        <v>240</v>
+      </c>
+      <c r="E45" s="9">
+        <v>90</v>
+      </c>
+      <c r="F45" s="9">
+        <v>300</v>
+      </c>
+      <c r="G45" s="9">
+        <v>6</v>
+      </c>
+      <c r="H45" s="9">
+        <v>110</v>
+      </c>
+      <c r="I45" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J45" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
+        <v>230</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B46" s="9">
+        <v>360</v>
+      </c>
+      <c r="C46" s="9">
+        <v>40</v>
+      </c>
+      <c r="D46" s="9">
+        <v>180</v>
+      </c>
+      <c r="E46" s="9">
+        <v>180</v>
+      </c>
+      <c r="F46" s="9">
+        <v>400</v>
+      </c>
+      <c r="G46" s="9">
+        <v>7</v>
+      </c>
+      <c r="H46" s="9">
+        <v>100</v>
+      </c>
+      <c r="I46" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J46" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="12"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
+        <v>180</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B47" s="9">
+        <v>400</v>
+      </c>
+      <c r="C47" s="9">
+        <v>55</v>
+      </c>
+      <c r="D47" s="9">
+        <v>200</v>
+      </c>
+      <c r="E47" s="9">
+        <v>220</v>
+      </c>
+      <c r="F47" s="9">
+        <v>350</v>
+      </c>
+      <c r="G47" s="9">
+        <v>6</v>
+      </c>
+      <c r="H47" s="9">
+        <v>30</v>
+      </c>
+      <c r="I47" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
+        <v>1255</v>
+      </c>
+      <c r="J47" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
+        <v>185</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>

--- a/DATA/12618749.xlsx
+++ b/DATA/12618749.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vivek Rai\Desktop\CAP776\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39A87ED5-6701-4BC6-8E44-7ACA9CD9DD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE52970F-EA08-441D-8579-32FDA581F05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="269" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t xml:space="preserve">back to back classes with busy schedule </t>
+  </si>
+  <si>
+    <t>one exttra class of c++ and do your mini project</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1049,7 @@
         <v>46249</v>
       </c>
       <c r="G3" s="13">
-        <v>46286</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -3043,27 +3046,51 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B48" s="9">
+        <v>450</v>
+      </c>
+      <c r="C48" s="9">
+        <v>60</v>
+      </c>
+      <c r="D48" s="9">
+        <v>240</v>
+      </c>
+      <c r="E48" s="9">
+        <v>180</v>
+      </c>
+      <c r="F48" s="9">
+        <v>50</v>
+      </c>
+      <c r="G48" s="9">
+        <v>1</v>
+      </c>
+      <c r="H48" s="9">
+        <v>60</v>
+      </c>
+      <c r="I48" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J48" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
